--- a/ZALO-PHUONG-AN.xlsx
+++ b/ZALO-PHUONG-AN.xlsx
@@ -11,6 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Tab quản trị mẫu tin" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Việc còn nợ + câu cần chốt" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Đã làm 05-08-2026" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. Ma trận kênh 24-08" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. Điểm loạn 24-08" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. Đề xuất + chốt" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1. So sánh App ↔ Zalo'!$A$5:$K$28</definedName>
@@ -22,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -122,8 +125,69 @@
       <color rgb="000B3B5C"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF1F3864"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FFC00000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF1F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="FF1F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFC00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF2E7D32"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFC00000"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -181,8 +245,43 @@
         <fgColor rgb="00FFF7ED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF0DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -252,11 +351,25 @@
         <color rgb="00C9DCEB"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -322,6 +435,81 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -618,6 +806,13 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>⚠️ BẢNG NÀY LÀ HIỆN TRẠNG NGÀY 05/08/2026 (app v5.9–v6.0). Tiêu đề tin nay đã chuyển hết sang TIẾNG ANH và có thêm kênh 🔵 BẢN TIN 08:00. Hiện trạng mới nhất ở sheet «6. Ma trận kênh 24-08».</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="31.5" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -2777,6 +2972,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>⚠️ Q1–Q5 dưới đây đặt ra ngày 05/08/2026 và vẫn CHƯA ai trả lời. Bốn câu mới của đợt rà 24/08/2026 (Q6–Q9) nằm ở sheet «8. Đề xuất + chốt».</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="31.5" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -3650,4 +3852,2347 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF1F3864"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>MA TRẬN KÊNH TIN ZALO — HIỆN TRẠNG 24/08/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>Rà thẳng từ mã nguồn ngày 24/08/2026 · app ?v=87 · js/21-notify.js + js/08-requests.js + zalo-gas/Code-MOI.gs. Bảng này THAY THẾ sheet «1. So sánh App ↔ Zalo» (bảng đó là hiện trạng 05/08/2026, tiêu đề còn tiếng Việt).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>🔴 NGAY = ≤60 giây, KHÔNG áp giờ im lặng  ·  🟡 GỘP = chờ 8 phút, CÓ áp giờ im lặng 21:30–06:30  ·  🔵 BẢN TIN = gom về 08:00 hôm sau (phải có người mở app)  ·  ⚪ CHỈ APP = không tốn tin Zalo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31.5" customHeight="1">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>Mã tin (kind / zk)</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>Sự kiện phát sinh</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>Người nhận</t>
+        </is>
+      </c>
+      <c r="E5" s="32" t="inlineStr">
+        <is>
+          <t>Kênh</t>
+        </is>
+      </c>
+      <c r="F5" s="32" t="inlineStr">
+        <is>
+          <t>Tiêu đề gửi đi (tiếng Anh)</t>
+        </is>
+      </c>
+      <c r="G5" s="32" t="inlineStr">
+        <is>
+          <t>Dòng "việc phải làm"</t>
+        </is>
+      </c>
+      <c r="H5" s="32" t="inlineStr">
+        <is>
+          <t>Nhóm gộp</t>
+        </is>
+      </c>
+      <c r="I5" s="32" t="inlineStr">
+        <is>
+          <t>Nguồn trong code</t>
+        </is>
+      </c>
+      <c r="J5" s="32" t="inlineStr">
+        <is>
+          <t>★ Ý KIẾN CỦA BẠN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21.75" customHeight="1">
+      <c r="A6" s="33" t="inlineStr">
+        <is>
+          <t>NHÓM A — CẦN NGƯỜI NHẬN BẤM XÁC NHẬN</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="n"/>
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="34" t="n"/>
+      <c r="E6" s="34" t="n"/>
+      <c r="F6" s="34" t="n"/>
+      <c r="G6" s="34" t="n"/>
+      <c r="H6" s="34" t="n"/>
+      <c r="I6" s="34" t="n"/>
+      <c r="J6" s="34" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B7" s="35" t="inlineStr">
+        <is>
+          <t>kind:'schedChange'</t>
+        </is>
+      </c>
+      <c r="C7" s="35" t="inlineStr">
+        <is>
+          <t>Quản lý / thư ký sửa ô LỊCH THỰC TẾ của một người</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="inlineStr">
+        <is>
+          <t>Nhân viên bị đổi ca</t>
+        </is>
+      </c>
+      <c r="E7" s="35" t="inlineStr">
+        <is>
+          <t>🔴 NGAY</t>
+        </is>
+      </c>
+      <c r="F7" s="35" t="inlineStr">
+        <is>
+          <t>📅 SHIFT CHANGED</t>
+        </is>
+      </c>
+      <c r="G7" s="35" t="inlineStr">
+        <is>
+          <t>Confirm in app</t>
+        </is>
+      </c>
+      <c r="H7" s="35" t="inlineStr">
+        <is>
+          <t>sched</t>
+        </is>
+      </c>
+      <c r="I7" s="35" t="inlineStr">
+        <is>
+          <t>06-calendar.js:366 emitSchedChange</t>
+        </is>
+      </c>
+      <c r="J7" s="36" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="inlineStr">
+        <is>
+          <t>kind:'swapConfirm'</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="inlineStr">
+        <is>
+          <t>A gửi đơn đổi ca với B</t>
+        </is>
+      </c>
+      <c r="D8" s="35" t="inlineStr">
+        <is>
+          <t>Nhân viên B</t>
+        </is>
+      </c>
+      <c r="E8" s="35" t="inlineStr">
+        <is>
+          <t>🔴 NGAY</t>
+        </is>
+      </c>
+      <c r="F8" s="35" t="inlineStr">
+        <is>
+          <t>🔄 SWAP REQUEST</t>
+        </is>
+      </c>
+      <c r="G8" s="35" t="inlineStr">
+        <is>
+          <t>Accept / decline in app</t>
+        </is>
+      </c>
+      <c r="H8" s="35" t="inlineStr">
+        <is>
+          <t>swap</t>
+        </is>
+      </c>
+      <c r="I8" s="35" t="inlineStr">
+        <is>
+          <t>13-portal.js:1965 — gắn nz:1, nội dung đã gộp vào tin apprNeed</t>
+        </is>
+      </c>
+      <c r="J8" s="36" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>kind:'coverConfirm'</t>
+        </is>
+      </c>
+      <c r="C9" s="35" t="inlineStr">
+        <is>
+          <t>Đơn tăng ca có nhờ người OT cover</t>
+        </is>
+      </c>
+      <c r="D9" s="35" t="inlineStr">
+        <is>
+          <t>Người được nhờ cover</t>
+        </is>
+      </c>
+      <c r="E9" s="35" t="inlineStr">
+        <is>
+          <t>🔴 NGAY</t>
+        </is>
+      </c>
+      <c r="F9" s="35" t="inlineStr">
+        <is>
+          <t>🙋 OT COVER REQUEST</t>
+        </is>
+      </c>
+      <c r="G9" s="35" t="inlineStr">
+        <is>
+          <t>Accept / decline in app</t>
+        </is>
+      </c>
+      <c r="H9" s="35" t="inlineStr">
+        <is>
+          <t>cover</t>
+        </is>
+      </c>
+      <c r="I9" s="35" t="inlineStr">
+        <is>
+          <t>13-portal.js:1983 · 08-requests.js:280 — nz:1</t>
+        </is>
+      </c>
+      <c r="J9" s="36" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>zk:'schedBulk'</t>
+        </is>
+      </c>
+      <c r="C10" s="35" t="inlineStr">
+        <is>
+          <t>Quản lý bấm 🔕 Giữ, sửa lịch nhiều người, rồi bấm 🔔 Gửi</t>
+        </is>
+      </c>
+      <c r="D10" s="35" t="inlineStr">
+        <is>
+          <t>Từng người bị sửa lịch</t>
+        </is>
+      </c>
+      <c r="E10" s="35" t="inlineStr">
+        <is>
+          <t>🔴 NGAY</t>
+        </is>
+      </c>
+      <c r="F10" s="35" t="inlineStr">
+        <is>
+          <t>📅 SCHEDULE UPDATED — n people / m changes</t>
+        </is>
+      </c>
+      <c r="G10" s="35" t="inlineStr">
+        <is>
+          <t>Confirm in app</t>
+        </is>
+      </c>
+      <c r="H10" s="35" t="inlineStr">
+        <is>
+          <t>sched</t>
+        </is>
+      </c>
+      <c r="I10" s="35" t="inlineStr">
+        <is>
+          <t>06-calendar.js:482 schedHoldFlush</t>
+        </is>
+      </c>
+      <c r="J10" s="36" t="n"/>
+    </row>
+    <row r="11" ht="21.75" customHeight="1">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>NHÓM B — KẾT QUẢ DUYỆT ĐƠN  (đều đi chung kind:'info', phân biệt bằng zk)</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n"/>
+      <c r="H11" s="34" t="n"/>
+      <c r="I11" s="34" t="n"/>
+      <c r="J11" s="34" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="37" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>zk:'fe'</t>
+        </is>
+      </c>
+      <c r="C12" s="37" t="inlineStr">
+        <is>
+          <t>Field Engineer duyệt xong, đơn lên cấp trên</t>
+        </is>
+      </c>
+      <c r="D12" s="37" t="inlineStr">
+        <is>
+          <t>Các bên liên quan</t>
+        </is>
+      </c>
+      <c r="E12" s="37" t="inlineStr">
+        <is>
+          <t>⚪ CHỈ APP</t>
+        </is>
+      </c>
+      <c r="F12" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="37" t="inlineStr">
+        <is>
+          <t>Quy tắc R1 — bỏ tin trạng thái trung gian</t>
+        </is>
+      </c>
+      <c r="J12" s="36" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="37" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B13" s="37" t="inlineStr">
+        <is>
+          <t>zk:'provapproved'</t>
+        </is>
+      </c>
+      <c r="C13" s="37" t="inlineStr">
+        <is>
+          <t>Section Chief duyệt (v7.9: đây LÀ đã duyệt)</t>
+        </is>
+      </c>
+      <c r="D13" s="37" t="inlineStr">
+        <is>
+          <t>Các bên liên quan</t>
+        </is>
+      </c>
+      <c r="E13" s="37" t="inlineStr">
+        <is>
+          <t>⚪ CHỈ APP</t>
+        </is>
+      </c>
+      <c r="F13" s="37" t="inlineStr">
+        <is>
+          <t>— (đi chung zk:'approved')</t>
+        </is>
+      </c>
+      <c r="G13" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="37" t="inlineStr">
+        <is>
+          <t>08-requests.js:1645 notifyReqParties — zk đổi thành 'approved'</t>
+        </is>
+      </c>
+      <c r="J13" s="36" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="38" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B14" s="38" t="inlineStr">
+        <is>
+          <t>zk:'approved'</t>
+        </is>
+      </c>
+      <c r="C14" s="38" t="inlineStr">
+        <is>
+          <t>Đơn được duyệt</t>
+        </is>
+      </c>
+      <c r="D14" s="38" t="inlineStr">
+        <is>
+          <t>Các bên liên quan</t>
+        </is>
+      </c>
+      <c r="E14" s="38" t="inlineStr">
+        <is>
+          <t>🔴 NGAY  hoặc  🔵 BẢN TIN</t>
+        </is>
+      </c>
+      <c r="F14" s="38" t="inlineStr">
+        <is>
+          <t>✅ APPROVED</t>
+        </is>
+      </c>
+      <c r="G14" s="38" t="inlineStr">
+        <is>
+          <t>(không có)</t>
+        </is>
+      </c>
+      <c r="H14" s="38" t="inlineStr">
+        <is>
+          <t>reqResult</t>
+        </is>
+      </c>
+      <c r="I14" s="38" t="inlineStr">
+        <is>
+          <t>21-notify.js:840 digestApplies — ⚠️ đơn ot/multi/late/wt bị hạ xuống bản tin 08:00, đơn nghỉ phép/đổi ca bắn ngay. Xem L2.</t>
+        </is>
+      </c>
+      <c r="J14" s="36" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>zk:'rejected'</t>
+        </is>
+      </c>
+      <c r="C15" s="35" t="inlineStr">
+        <is>
+          <t>Đơn bị từ chối</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="inlineStr">
+        <is>
+          <t>Các bên liên quan</t>
+        </is>
+      </c>
+      <c r="E15" s="35" t="inlineStr">
+        <is>
+          <t>🔴 NGAY</t>
+        </is>
+      </c>
+      <c r="F15" s="35" t="inlineStr">
+        <is>
+          <t>❌ REJECTED</t>
+        </is>
+      </c>
+      <c r="G15" s="35" t="inlineStr">
+        <is>
+          <t>Submit a new request if needed</t>
+        </is>
+      </c>
+      <c r="H15" s="35" t="inlineStr">
+        <is>
+          <t>reqResult</t>
+        </is>
+      </c>
+      <c r="I15" s="35" t="inlineStr">
+        <is>
+          <t>Cố ý giữ NGAY: bị từ chối mà biết muộn thì đi làm thừa</t>
+        </is>
+      </c>
+      <c r="J15" s="36" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>zk:'revoked'</t>
+        </is>
+      </c>
+      <c r="C16" s="35" t="inlineStr">
+        <is>
+          <t>Huỷ duyệt một đơn đã duyệt</t>
+        </is>
+      </c>
+      <c r="D16" s="35" t="inlineStr">
+        <is>
+          <t>Các bên liên quan</t>
+        </is>
+      </c>
+      <c r="E16" s="35" t="inlineStr">
+        <is>
+          <t>🔴 NGAY</t>
+        </is>
+      </c>
+      <c r="F16" s="35" t="inlineStr">
+        <is>
+          <t>↩️ APPROVAL WITHDRAWN</t>
+        </is>
+      </c>
+      <c r="G16" s="35" t="inlineStr">
+        <is>
+          <t>(không có)</t>
+        </is>
+      </c>
+      <c r="H16" s="35" t="inlineStr">
+        <is>
+          <t>reqResult</t>
+        </is>
+      </c>
+      <c r="I16" s="35" t="inlineStr">
+        <is>
+          <t>Cố ý giữ NGAY — lịch vừa bị đổi ngược</t>
+        </is>
+      </c>
+      <c r="J16" s="36" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="38" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B17" s="38" t="inlineStr">
+        <is>
+          <t>zk:'cancelled'</t>
+        </is>
+      </c>
+      <c r="C17" s="38" t="inlineStr">
+        <is>
+          <t>Đơn bị huỷ</t>
+        </is>
+      </c>
+      <c r="D17" s="38" t="inlineStr">
+        <is>
+          <t>Các bên liên quan</t>
+        </is>
+      </c>
+      <c r="E17" s="38" t="inlineStr">
+        <is>
+          <t>🟡 GỘP  hoặc  🔵 BẢN TIN</t>
+        </is>
+      </c>
+      <c r="F17" s="38" t="inlineStr">
+        <is>
+          <t>🗑️ REQUEST CANCELLED</t>
+        </is>
+      </c>
+      <c r="G17" s="38" t="inlineStr">
+        <is>
+          <t>(không có)</t>
+        </is>
+      </c>
+      <c r="H17" s="38" t="inlineStr">
+        <is>
+          <t>reqResult</t>
+        </is>
+      </c>
+      <c r="I17" s="38" t="inlineStr">
+        <is>
+          <t>Cũng bị digestApplies hạ kênh như B3</t>
+        </is>
+      </c>
+      <c r="J17" s="36" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="37" t="inlineStr">
+        <is>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="B18" s="37" t="inlineStr">
+        <is>
+          <t>zk:'final'</t>
+        </is>
+      </c>
+      <c r="C18" s="37" t="inlineStr">
+        <is>
+          <t>Quản lý người Hàn ghi nhận đơn đã duyệt</t>
+        </is>
+      </c>
+      <c r="D18" s="37" t="inlineStr">
+        <is>
+          <t>Các bên liên quan</t>
+        </is>
+      </c>
+      <c r="E18" s="37" t="inlineStr">
+        <is>
+          <t>⚪ CHỈ APP</t>
+        </is>
+      </c>
+      <c r="F18" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="37" t="inlineStr">
+        <is>
+          <t>Không báo "đã duyệt" hai lần cho cùng một đơn</t>
+        </is>
+      </c>
+      <c r="J18" s="36" t="n"/>
+    </row>
+    <row r="19" ht="21.75" customHeight="1">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>NHÓM C — PHẢN HỒI HAI CHIỀU GIỮA NHÂN VIÊN</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="34" t="n"/>
+      <c r="E19" s="34" t="n"/>
+      <c r="F19" s="34" t="n"/>
+      <c r="G19" s="34" t="n"/>
+      <c r="H19" s="34" t="n"/>
+      <c r="I19" s="34" t="n"/>
+      <c r="J19" s="34" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B20" s="35" t="inlineStr">
+        <is>
+          <t>zk:'schedDecline'</t>
+        </is>
+      </c>
+      <c r="C20" s="35" t="inlineStr">
+        <is>
+          <t>Nhân viên TỪ CHỐI thay đổi lịch</t>
+        </is>
+      </c>
+      <c r="D20" s="35" t="inlineStr">
+        <is>
+          <t>Người tạo thay đổi</t>
+        </is>
+      </c>
+      <c r="E20" s="35" t="inlineStr">
+        <is>
+          <t>🟡 GỘP</t>
+        </is>
+      </c>
+      <c r="F20" s="35" t="inlineStr">
+        <is>
+          <t>⚠️ CHANGE DECLINED</t>
+        </is>
+      </c>
+      <c r="G20" s="35" t="inlineStr">
+        <is>
+          <t>(không có)</t>
+        </is>
+      </c>
+      <c r="H20" s="35" t="inlineStr">
+        <is>
+          <t>sched</t>
+        </is>
+      </c>
+      <c r="I20" s="35" t="inlineStr">
+        <is>
+          <t>13-portal.js:536</t>
+        </is>
+      </c>
+      <c r="J20" s="36" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>zk:'schedRevoke'</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="inlineStr">
+        <is>
+          <t>Quản lý THU HỒI thay đổi lịch đã gửi</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="inlineStr">
+        <is>
+          <t>Nhân viên</t>
+        </is>
+      </c>
+      <c r="E21" s="35" t="inlineStr">
+        <is>
+          <t>🔴 NGAY</t>
+        </is>
+      </c>
+      <c r="F21" s="35" t="inlineStr">
+        <is>
+          <t>↩️ CHANGE WITHDRAWN</t>
+        </is>
+      </c>
+      <c r="G21" s="35" t="inlineStr">
+        <is>
+          <t>(không có)</t>
+        </is>
+      </c>
+      <c r="H21" s="35" t="inlineStr">
+        <is>
+          <t>sched</t>
+        </is>
+      </c>
+      <c r="I21" s="35" t="inlineStr">
+        <is>
+          <t>13-portal.js:490</t>
+        </is>
+      </c>
+      <c r="J21" s="36" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="37" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B22" s="37" t="inlineStr">
+        <is>
+          <t>zk:'swapOk'</t>
+        </is>
+      </c>
+      <c r="C22" s="37" t="inlineStr">
+        <is>
+          <t>B đồng ý đổi ca</t>
+        </is>
+      </c>
+      <c r="D22" s="37" t="inlineStr">
+        <is>
+          <t>Người xin đổi (A)</t>
+        </is>
+      </c>
+      <c r="E22" s="37" t="inlineStr">
+        <is>
+          <t>⚪ CHỈ APP</t>
+        </is>
+      </c>
+      <c r="F22" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" s="37" t="inlineStr">
+        <is>
+          <t>Tin tốt xuôi chiều — không cần làm gì</t>
+        </is>
+      </c>
+      <c r="J22" s="36" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B23" s="35" t="inlineStr">
+        <is>
+          <t>zk:'swapNo'</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="inlineStr">
+        <is>
+          <t>B từ chối đổi ca</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="inlineStr">
+        <is>
+          <t>Người xin đổi (A)</t>
+        </is>
+      </c>
+      <c r="E23" s="35" t="inlineStr">
+        <is>
+          <t>🔴 NGAY</t>
+        </is>
+      </c>
+      <c r="F23" s="35" t="inlineStr">
+        <is>
+          <t>❌ SWAP DECLINED</t>
+        </is>
+      </c>
+      <c r="G23" s="35" t="inlineStr">
+        <is>
+          <t>Choose another colleague</t>
+        </is>
+      </c>
+      <c r="H23" s="35" t="inlineStr">
+        <is>
+          <t>swap</t>
+        </is>
+      </c>
+      <c r="I23" s="35" t="inlineStr">
+        <is>
+          <t>13-portal.js:560</t>
+        </is>
+      </c>
+      <c r="J23" s="36" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="37" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B24" s="37" t="inlineStr">
+        <is>
+          <t>zk:'coverOk'</t>
+        </is>
+      </c>
+      <c r="C24" s="37" t="inlineStr">
+        <is>
+          <t>Người cover nhận lời nhờ</t>
+        </is>
+      </c>
+      <c r="D24" s="37" t="inlineStr">
+        <is>
+          <t>Người nhờ (A)</t>
+        </is>
+      </c>
+      <c r="E24" s="37" t="inlineStr">
+        <is>
+          <t>⚪ CHỈ APP</t>
+        </is>
+      </c>
+      <c r="F24" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" s="37" t="inlineStr">
+        <is>
+          <t>Tin tốt xuôi chiều</t>
+        </is>
+      </c>
+      <c r="J24" s="36" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="35" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B25" s="35" t="inlineStr">
+        <is>
+          <t>zk:'coverNo'</t>
+        </is>
+      </c>
+      <c r="C25" s="35" t="inlineStr">
+        <is>
+          <t>Người cover từ chối</t>
+        </is>
+      </c>
+      <c r="D25" s="35" t="inlineStr">
+        <is>
+          <t>Người nhờ (A)</t>
+        </is>
+      </c>
+      <c r="E25" s="35" t="inlineStr">
+        <is>
+          <t>🔴 NGAY</t>
+        </is>
+      </c>
+      <c r="F25" s="35" t="inlineStr">
+        <is>
+          <t>❌ OT COVER DECLINED</t>
+        </is>
+      </c>
+      <c r="G25" s="35" t="inlineStr">
+        <is>
+          <t>Assign another colleague</t>
+        </is>
+      </c>
+      <c r="H25" s="35" t="inlineStr">
+        <is>
+          <t>cover</t>
+        </is>
+      </c>
+      <c r="I25" s="35" t="inlineStr">
+        <is>
+          <t>13-portal.js:589</t>
+        </is>
+      </c>
+      <c r="J25" s="36" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="35" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B26" s="35" t="inlineStr">
+        <is>
+          <t>zk:'coverRemoved'</t>
+        </is>
+      </c>
+      <c r="C26" s="35" t="inlineStr">
+        <is>
+          <t>Bị gỡ khỏi vai trò OT cover</t>
+        </is>
+      </c>
+      <c r="D26" s="35" t="inlineStr">
+        <is>
+          <t>Người cover CŨ</t>
+        </is>
+      </c>
+      <c r="E26" s="35" t="inlineStr">
+        <is>
+          <t>🟡 GỘP</t>
+        </is>
+      </c>
+      <c r="F26" s="35" t="inlineStr">
+        <is>
+          <t>ℹ️ OT COVER REMOVED</t>
+        </is>
+      </c>
+      <c r="G26" s="35" t="inlineStr">
+        <is>
+          <t>(không có)</t>
+        </is>
+      </c>
+      <c r="H26" s="35" t="inlineStr">
+        <is>
+          <t>cover</t>
+        </is>
+      </c>
+      <c r="I26" s="35" t="inlineStr">
+        <is>
+          <t>08-requests.js:270</t>
+        </is>
+      </c>
+      <c r="J26" s="36" t="n"/>
+    </row>
+    <row r="27" ht="21.75" customHeight="1">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>NHÓM D — SỰ KIỆN TRÊN LỊCH</t>
+        </is>
+      </c>
+      <c r="B27" s="34" t="n"/>
+      <c r="C27" s="34" t="n"/>
+      <c r="D27" s="34" t="n"/>
+      <c r="E27" s="34" t="n"/>
+      <c r="F27" s="34" t="n"/>
+      <c r="G27" s="34" t="n"/>
+      <c r="H27" s="34" t="n"/>
+      <c r="I27" s="34" t="n"/>
+      <c r="J27" s="34" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="35" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B28" s="35" t="inlineStr">
+        <is>
+          <t>kind:'event'</t>
+        </is>
+      </c>
+      <c r="C28" s="35" t="inlineStr">
+        <is>
+          <t>Quản trị bấm gửi một sự kiện trên lịch</t>
+        </is>
+      </c>
+      <c r="D28" s="35" t="inlineStr">
+        <is>
+          <t>Theo phạm vi: tất cả / theo ca / chọn tay</t>
+        </is>
+      </c>
+      <c r="E28" s="35" t="inlineStr">
+        <is>
+          <t>🟡 GỘP</t>
+        </is>
+      </c>
+      <c r="F28" s="35" t="inlineStr">
+        <is>
+          <t>📢 ANNOUNCEMENT</t>
+        </is>
+      </c>
+      <c r="G28" s="35" t="inlineStr">
+        <is>
+          <t>(không có)</t>
+        </is>
+      </c>
+      <c r="H28" s="35" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="I28" s="35" t="inlineStr">
+        <is>
+          <t>20-events.js:210 — fan-out 23 tin nay đã được hộp gửi gộp thành 1 (zaloOutMergeFp)</t>
+        </is>
+      </c>
+      <c r="J28" s="36" t="n"/>
+    </row>
+    <row r="29" ht="21.75" customHeight="1">
+      <c r="A29" s="33" t="inlineStr">
+        <is>
+          <t>NHÓM E — BÁO CHO NGƯỜI DUYỆT</t>
+        </is>
+      </c>
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="34" t="n"/>
+      <c r="D29" s="34" t="n"/>
+      <c r="E29" s="34" t="n"/>
+      <c r="F29" s="34" t="n"/>
+      <c r="G29" s="34" t="n"/>
+      <c r="H29" s="34" t="n"/>
+      <c r="I29" s="34" t="n"/>
+      <c r="J29" s="34" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="38" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B30" s="38" t="inlineStr">
+        <is>
+          <t>zk:'apprNeed'</t>
+        </is>
+      </c>
+      <c r="C30" s="38" t="inlineStr">
+        <is>
+          <t>Đơn chuyển sang một cấp duyệt mới</t>
+        </is>
+      </c>
+      <c r="D30" s="38" t="inlineStr">
+        <is>
+          <t>Cấp đang chờ + Hoàng Trung</t>
+        </is>
+      </c>
+      <c r="E30" s="38" t="inlineStr">
+        <is>
+          <t>🔴 NGAY  hoặc  🔵 BẢN TIN</t>
+        </is>
+      </c>
+      <c r="F30" s="38" t="inlineStr">
+        <is>
+          <t>📥 APPROVAL REQUIRED — &lt;cấp&gt;</t>
+        </is>
+      </c>
+      <c r="G30" s="38" t="inlineStr">
+        <is>
+          <t>Approve in app</t>
+        </is>
+      </c>
+      <c r="H30" s="38" t="inlineStr">
+        <is>
+          <t>apprNeed</t>
+        </is>
+      </c>
+      <c r="I30" s="38" t="inlineStr">
+        <is>
+          <t>08-requests.js:1613 notifyApprovers — ⚠️ 1 thông báo cho MỖI người duyệt, cùng reqId. Nguồn của L1.</t>
+        </is>
+      </c>
+      <c r="J30" s="36" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="35" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B31" s="35" t="inlineStr">
+        <is>
+          <t>zk:'finalNote'</t>
+        </is>
+      </c>
+      <c r="C31" s="35" t="inlineStr">
+        <is>
+          <t>Mời Quản lý người Hàn ghi nhận (v8.1: MỌI việc của cấp cuối)</t>
+        </is>
+      </c>
+      <c r="D31" s="35" t="inlineStr">
+        <is>
+          <t>Quản lý người Hàn / người được uỷ quyền</t>
+        </is>
+      </c>
+      <c r="E31" s="35" t="inlineStr">
+        <is>
+          <t>🔵 BẢN TIN 08:00</t>
+        </is>
+      </c>
+      <c r="F31" s="35" t="inlineStr">
+        <is>
+          <t>🧾 FOR REVIEW</t>
+        </is>
+      </c>
+      <c r="G31" s="35" t="inlineStr">
+        <is>
+          <t>(cố ý không có)</t>
+        </is>
+      </c>
+      <c r="H31" s="35" t="inlineStr">
+        <is>
+          <t>finalNote</t>
+        </is>
+      </c>
+      <c r="I31" s="35" t="inlineStr">
+        <is>
+          <t>08-requests.js:1613 · gói riêng dựng bằng dgReviewLines() — có lọc trùng reqId</t>
+        </is>
+      </c>
+      <c r="J31" s="36" t="n"/>
+    </row>
+    <row r="32" ht="21.75" customHeight="1">
+      <c r="A32" s="33" t="inlineStr">
+        <is>
+          <t>NHÓM G — LỊCH ĐÀO TẠO</t>
+        </is>
+      </c>
+      <c r="B32" s="34" t="n"/>
+      <c r="C32" s="34" t="n"/>
+      <c r="D32" s="34" t="n"/>
+      <c r="E32" s="34" t="n"/>
+      <c r="F32" s="34" t="n"/>
+      <c r="G32" s="34" t="n"/>
+      <c r="H32" s="34" t="n"/>
+      <c r="I32" s="34" t="n"/>
+      <c r="J32" s="34" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="35" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+      <c r="B33" s="35" t="inlineStr">
+        <is>
+          <t>kind:'training'</t>
+        </is>
+      </c>
+      <c r="C33" s="35" t="inlineStr">
+        <is>
+          <t>Xếp / sửa một buổi đào tạo</t>
+        </is>
+      </c>
+      <c r="D33" s="35" t="inlineStr">
+        <is>
+          <t>Người đi học + cấp duyệt</t>
+        </is>
+      </c>
+      <c r="E33" s="35" t="inlineStr">
+        <is>
+          <t>🟡 GỘP</t>
+        </is>
+      </c>
+      <c r="F33" s="35" t="inlineStr">
+        <is>
+          <t>🎓 TRAINING SCHEDULE</t>
+        </is>
+      </c>
+      <c r="G33" s="35" t="inlineStr">
+        <is>
+          <t>See the training schedule in app</t>
+        </is>
+      </c>
+      <c r="H33" s="35" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="I33" s="35" t="inlineStr">
+        <is>
+          <t>22-training.js:608 · 8 người sinh 8 thông báo nhưng chỉ tốn 1 tin Zalo</t>
+        </is>
+      </c>
+      <c r="J33" s="36" t="n"/>
+    </row>
+    <row r="35" ht="21.75" customHeight="1">
+      <c r="A35" s="39" t="inlineStr">
+        <is>
+          <t>TỔNG: 22 loại tin  ·  17 loại có gửi Zalo  ·  11 / 17 đang ở kênh 🔴 NGAY  ·  3 loại (apprNeed / approved / cancelled) ĐỔI KÊNH tuỳ loại đơn</t>
+        </is>
+      </c>
+      <c r="B35" s="34" t="n"/>
+      <c r="C35" s="34" t="n"/>
+      <c r="D35" s="34" t="n"/>
+      <c r="E35" s="34" t="n"/>
+      <c r="F35" s="34" t="n"/>
+      <c r="G35" s="34" t="n"/>
+      <c r="H35" s="34" t="n"/>
+      <c r="I35" s="34" t="n"/>
+      <c r="J35" s="34" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A11:J11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FFC00000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>ĐIỂM GÂY LOẠN — 12 MỤC, XẾP THEO MỨC ĐỘ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>Rà ngày 24/08/2026 trên bản ?v=87. Cột "Sửa bằng" trỏ sang sheet «8. Đề xuất + câu cần chốt».</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>NẶNG = người dùng thấy ngay mỗi ngày  ·  LỖI MÃ = mã chạy sai so với ý định  ·  THIẾT KẾ = mã chạy đúng ý định nhưng ý định gây rối  ·  NHỎ = hiếm gặp / là giới hạn đã biết</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31.5" customHeight="1">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>Mức</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>Điểm loạn</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>Ở đâu trong code</t>
+        </is>
+      </c>
+      <c r="E5" s="32" t="inlineStr">
+        <is>
+          <t>Nguyên nhân</t>
+        </is>
+      </c>
+      <c r="F5" s="32" t="inlineStr">
+        <is>
+          <t>Hệ quả thấy được</t>
+        </is>
+      </c>
+      <c r="G5" s="32" t="inlineStr">
+        <is>
+          <t>Sửa bằng</t>
+        </is>
+      </c>
+      <c r="H5" s="32" t="inlineStr">
+        <is>
+          <t>★ Ý KIẾN CỦA BẠN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="40" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B6" s="41" t="inlineStr">
+        <is>
+          <t>NẶNG</t>
+        </is>
+      </c>
+      <c r="C6" s="40" t="inlineStr">
+        <is>
+          <t>Bản tin 08:00 lặp lại y nguyên một đơn nhiều lần</t>
+        </is>
+      </c>
+      <c r="D6" s="42" t="inlineStr">
+        <is>
+          <t>js/21-notify.js:1049 digestBuild()</t>
+        </is>
+      </c>
+      <c r="E6" s="43" t="inlineStr">
+        <is>
+          <t>notifyApprovers() sinh 1 thông báo cho MỖI người duyệt; notifyReqParties() sinh 1 cho MỖI bên liên quan. Tất cả cùng reqId và lines dựng từ chính đơn nên giống hệt nhau. Kênh NGAY thoát nhờ zaloOutMergeFp gộp trùng vân tay, nhưng sổ chờ digest KHÔNG có bước lọc trùng nào — digestBuild chỉ nối các khối bằng "— — —".</t>
+        </is>
+      </c>
+      <c r="F6" s="43" t="inlineStr">
+        <is>
+          <t>Một đơn OT có 2 Field Engineer + Hoàng Trung → khối dòng của đơn đó xuất hiện 3 LẦN trong 📥 DAILY DIGEST. Tệ hơn: DIGEST_MAX_LINES=60 bị dòng lặp ăn hết, dòng "… and N more line(s)" cắt mất ĐƠN THẬT ở cuối. (Gói finalNote thoát nạn vì dgReviewLines() có sổ seen[id].)</t>
+        </is>
+      </c>
+      <c r="G6" s="44" t="inlineStr">
+        <is>
+          <t>Đ1</t>
+        </is>
+      </c>
+      <c r="H6" s="36" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="40" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>NẶNG</t>
+        </is>
+      </c>
+      <c r="C7" s="40" t="inlineStr">
+        <is>
+          <t>Cùng một loại tin: lúc bắn ngay, lúc để sáng mai</t>
+        </is>
+      </c>
+      <c r="D7" s="42" t="inlineStr">
+        <is>
+          <t>js/21-notify.js:840 digestApplies() · DIGEST_REQ_TYPES</t>
+        </is>
+      </c>
+      <c r="E7" s="43" t="inlineStr">
+        <is>
+          <t>Kênh của 'approved' khai là NGAY, nhưng digestApplies() hạ xuống BẢN TIN khi đơn thuộc ot/multi/late/wt. Quyết định "gấp hay không gấp" đang dựa vào LOẠI ĐƠN, trong khi người đọc chỉ nhìn thấy LOẠI TIN.</t>
+        </is>
+      </c>
+      <c r="F7" s="43" t="inlineStr">
+        <is>
+          <t>15:00 duyệt đơn nghỉ phép → ✅ APPROVED tới ngay. 15:00 duyệt đơn tăng ca → ✅ APPROVED tới 08:00 SÁNG MAI. Tiêu đề giống hệt nhau. Không ai trong nhóm suy ra được luật, và bắt đầu bỏ qua tin.</t>
+        </is>
+      </c>
+      <c r="G7" s="44" t="inlineStr">
+        <is>
+          <t>Đ2, Đ3</t>
+        </is>
+      </c>
+      <c r="H7" s="36" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="40" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="B8" s="41" t="inlineStr">
+        <is>
+          <t>NẶNG</t>
+        </is>
+      </c>
+      <c r="C8" s="40" t="inlineStr">
+        <is>
+          <t>Ba đồng hồ chạy song song, không cái nào biết cái nào</t>
+        </is>
+      </c>
+      <c r="D8" s="42" t="inlineStr">
+        <is>
+          <t>Code-MOI.gs:66–68 · js/21-notify.js:145 DIGEST_HOUR</t>
+        </is>
+      </c>
+      <c r="E8" s="43" t="inlineStr">
+        <is>
+          <t>NGAY: ≤60 giây, KHÔNG áp giờ im lặng. GỘP: 8 phút, CÓ áp giờ im lặng nên tin sinh lúc 22:00 nằm chờ tới 06:30 rồi bung một cụm. BẢN TIN: 08:00 và chỉ chạy khi có người mở app. Thêm: giờ im lặng đo bằng Session.getScriptTimeZone() của Apps Script, digestDayKey() đo bằng đồng hồ MÁY NHÂN VIÊN — hai đồng hồ.</t>
+        </is>
+      </c>
+      <c r="F8" s="43" t="inlineStr">
+        <is>
+          <t>Bốn cụm tin mỗi ngày ở bốn thời điểm khác nhau, hai trong số đó không đoán trước được: cụm 06:30 (batch tồn đêm) + cụm 08:00 (bản tin) + tin lẻ cả ngày + tin đêm (NGAY không bị chặn). Đây là cảm giác "loạn" rõ nhất.</t>
+        </is>
+      </c>
+      <c r="G8" s="44" t="inlineStr">
+        <is>
+          <t>Đ2, Đ10</t>
+        </is>
+      </c>
+      <c r="H8" s="36" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="45" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="B9" s="46" t="inlineStr">
+        <is>
+          <t>LỖI MÃ</t>
+        </is>
+      </c>
+      <c r="C9" s="45" t="inlineStr">
+        <is>
+          <t>zaloOutMergeSame chỉ gộp được tin trùng tiêu đề với tin ĐẦU TIÊN</t>
+        </is>
+      </c>
+      <c r="D9" s="47" t="inlineStr">
+        <is>
+          <t>js/21-notify.js:692</t>
+        </is>
+      </c>
+      <c r="E9" s="38" t="inlineStr">
+        <is>
+          <t>Dòng: if(!lead||lead.title!==it.title){ if(!lead)byKey[k]=it; out.push(it); return; } — khi lead ĐÃ CÓ mà tiêu đề khác, `it` được đẩy ra ngoài nhưng KHÔNG BAO GIỜ được ghi vào byKey. Tin thứ ba cùng tiêu đề với `it` lại đem so với lead → lại lệch → lại tách.</t>
+        </is>
+      </c>
+      <c r="F9" s="38" t="inlineStr">
+        <is>
+          <t>Mỗi khoá tos|group|pri|bcast chỉ gộp được đúng MỘT tiêu đề. Phép gộp thứ ba — cái đáng lẽ dồn nhiều việc của cùng một người thành một tin nhiều mục — gần như không chạy.</t>
+        </is>
+      </c>
+      <c r="G9" s="48" t="inlineStr">
+        <is>
+          <t>Đ5</t>
+        </is>
+      </c>
+      <c r="H9" s="36" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="45" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="B10" s="46" t="inlineStr">
+        <is>
+          <t>THIẾT KẾ</t>
+        </is>
+      </c>
+      <c r="C10" s="45" t="inlineStr">
+        <is>
+          <t>Tiêu đề mang số liệu động phá mọi phép gộp phía sau</t>
+        </is>
+      </c>
+      <c r="D10" s="47" t="inlineStr">
+        <is>
+          <t>js/21-notify.js:510 zaloTitle() · Code-MOI.gs:386</t>
+        </is>
+      </c>
+      <c r="E10" s="38" t="inlineStr">
+        <is>
+          <t>zaloFp() băm group|title|lines|action; Apps Script gộp theo to|group|title. Cả hai ĐỀU lấy tiêu đề. Nhưng tiêu đề lại chứa số đếm và tên cấp: "— 3 people / 7 changes", "— Section Chief", "· 5 item(s) · 12/08".</t>
+        </is>
+      </c>
+      <c r="F10" s="38" t="inlineStr">
+        <is>
+          <t>"📅 SCHEDULE UPDATED — 3 people / 7 changes" và "… / 8 changes" thành 2 tin. "📥 APPROVAL REQUIRED — Section Chief" và "— Field Engineer" cũng thành 2 tin cho cùng một đơn.</t>
+        </is>
+      </c>
+      <c r="G10" s="48" t="inlineStr">
+        <is>
+          <t>Đ4</t>
+        </is>
+      </c>
+      <c r="H10" s="36" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="45" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="B11" s="46" t="inlineStr">
+        <is>
+          <t>THIẾT KẾ</t>
+        </is>
+      </c>
+      <c r="C11" s="45" t="inlineStr">
+        <is>
+          <t>Bốn kiểu xưng người nhận trong cùng một chat</t>
+        </is>
+      </c>
+      <c r="D11" s="47" t="inlineStr">
+        <is>
+          <t>Code-MOI.gs:452 buildText_() · zaloAudienceName()</t>
+        </is>
+      </c>
+      <c r="E11" s="38" t="inlineStr">
+        <is>
+          <t>Mọi tin đổ vào MỘT chat nhóm duy nhất, nên dòng "👤 Tên" không còn là "gửi cho ai" mà là "tin này nói về ai" — mà nó chỉ xuất hiện khi bcast=0.</t>
+        </is>
+      </c>
+      <c r="F11" s="38" t="inlineStr">
+        <is>
+          <t>Bốn kiểu chạy song song: "👤 Tên" · "For: A · B · C" · "3 employees" · không có dòng nào. Người đọc không có chỗ cố định để dò xem tin có liên quan tới mình không.</t>
+        </is>
+      </c>
+      <c r="G11" s="48" t="inlineStr">
+        <is>
+          <t>Đ6</t>
+        </is>
+      </c>
+      <c r="H11" s="36" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="45" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="B12" s="46" t="inlineStr">
+        <is>
+          <t>THIẾT KẾ</t>
+        </is>
+      </c>
+      <c r="C12" s="45" t="inlineStr">
+        <is>
+          <t>Mỗi tin đính kèm link app ở cuối</t>
+        </is>
+      </c>
+      <c r="D12" s="47" t="inlineStr">
+        <is>
+          <t>Code-MOI.gs:461</t>
+        </is>
+      </c>
+      <c r="E12" s="38" t="inlineStr">
+        <is>
+          <t>var url = prop_("APP_URL"); if (url) out.push(url); — không có điều kiện nào.</t>
+        </is>
+      </c>
+      <c r="F12" s="38" t="inlineStr">
+        <is>
+          <t>Zalo dựng khung xem trước cho mỗi link. 30 tin một ngày là 30 khung xem trước chen giữa nội dung thật; chat dài gấp đôi lượng thông tin thật. Link chỉ có nghĩa ở tin cần bấm vào app.</t>
+        </is>
+      </c>
+      <c r="G12" s="48" t="inlineStr">
+        <is>
+          <t>Đ7</t>
+        </is>
+      </c>
+      <c r="H12" s="36" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="49" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+      <c r="B13" s="50" t="inlineStr">
+        <is>
+          <t>THIẾT KẾ</t>
+        </is>
+      </c>
+      <c r="C13" s="49" t="inlineStr">
+        <is>
+          <t>17 emoji tiêu đề, không nhóm được bằng mắt</t>
+        </is>
+      </c>
+      <c r="D13" s="51" t="inlineStr">
+        <is>
+          <t>js/21-notify.js:215 ZALO_TITLE + 4 tiêu đề digest</t>
+        </is>
+      </c>
+      <c r="E13" s="35" t="inlineStr">
+        <is>
+          <t>📥 🧾 📅 🔄 🙋 📢 🎓 ✅ ❌ ↩️ 🗑️ ⚠️ ℹ️ — mỗi mã một emoji riêng, không có quy ước "emoji này = nhóm việc này".</t>
+        </is>
+      </c>
+      <c r="F13" s="35" t="inlineStr">
+        <is>
+          <t>Cuộn nhanh trên điện thoại không phân biệt được ↩️ CHANGE WITHDRAWN với ↩️ APPROVAL WITHDRAWN. Mất hẳn lợi thế lớn nhất của emoji: liếc một giây là biết tin thuộc loại nào.</t>
+        </is>
+      </c>
+      <c r="G13" s="52" t="inlineStr">
+        <is>
+          <t>Đ8</t>
+        </is>
+      </c>
+      <c r="H13" s="36" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="49" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="B14" s="50" t="inlineStr">
+        <is>
+          <t>LỖI MÃ</t>
+        </is>
+      </c>
+      <c r="C14" s="49" t="inlineStr">
+        <is>
+          <t>digestStale không soi lại approved và cancelled</t>
+        </is>
+      </c>
+      <c r="D14" s="51" t="inlineStr">
+        <is>
+          <t>js/21-notify.js:903</t>
+        </is>
+      </c>
+      <c r="E14" s="35" t="inlineStr">
+        <is>
+          <t>Hàm chỉ xét 'apprNeed' (đơn còn pending không) và 'finalNote' (cấp cuối ký chưa). Mục 'approved' nằm sổ chờ gần 17 tiếng mà không ai soi lại.</t>
+        </is>
+      </c>
+      <c r="F14" s="35" t="inlineStr">
+        <is>
+          <t>Đơn OT duyệt chiều nay, huỷ duyệt tối nay → sáng mai vẫn được báo "✅ APPROVED".</t>
+        </is>
+      </c>
+      <c r="G14" s="52" t="inlineStr">
+        <is>
+          <t>Đ9</t>
+        </is>
+      </c>
+      <c r="H14" s="36" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="49" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
+      <c r="B15" s="50" t="inlineStr">
+        <is>
+          <t>NHỎ</t>
+        </is>
+      </c>
+      <c r="C15" s="49" t="inlineStr">
+        <is>
+          <t>Đẩy lại cùng một thông báo ở hai lượt flush có thể ra hai tin</t>
+        </is>
+      </c>
+      <c r="D15" s="51" t="inlineStr">
+        <is>
+          <t>js/21-notify.js:707 zaloFlush()</t>
+        </is>
+      </c>
+      <c r="E15" s="35" t="inlineStr">
+        <is>
+          <t>Khoá hàng đợi là it.notifIds[0]. Lần flush đầu tin bị gộp dưới khoá của một notif khác; lần sau nó không bị gộp và ghi hàng mới theo chính notifId của nó. Hai hàng cùng tồn tại.</t>
+        </is>
+      </c>
+      <c r="F15" s="35" t="inlineStr">
+        <is>
+          <t>Sửa đi sửa lại một ô lịch qua nhiều cửa sổ 4 giây có thể ra tin trùng. Hiếm nhưng có thật.</t>
+        </is>
+      </c>
+      <c r="G15" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="36" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="49" t="inlineStr">
+        <is>
+          <t>L11</t>
+        </is>
+      </c>
+      <c r="B16" s="50" t="inlineStr">
+        <is>
+          <t>NHỎ</t>
+        </is>
+      </c>
+      <c r="C16" s="49" t="inlineStr">
+        <is>
+          <t>ONE_CHAT_DEDUPE chỉ gộp trong cùng một lượt quét</t>
+        </is>
+      </c>
+      <c r="D16" s="51" t="inlineStr">
+        <is>
+          <t>Code-MOI.gs:403</t>
+        </is>
+      </c>
+      <c r="E16" s="35" t="inlineStr">
+        <is>
+          <t>Nó chỉ soi những hàng ĐẾN LƯỢT trong lượt tick này. Hai tin trùng nội dung tới cách nhau 61 giây thì đều thoát.</t>
+        </is>
+      </c>
+      <c r="F16" s="35" t="inlineStr">
+        <is>
+          <t>Đây là lưới an toàn, KHÔNG phải cơ chế gộp. Đừng tính nó vào bài toán gom tin.</t>
+        </is>
+      </c>
+      <c r="G16" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="36" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="49" t="inlineStr">
+        <is>
+          <t>L12</t>
+        </is>
+      </c>
+      <c r="B17" s="50" t="inlineStr">
+        <is>
+          <t>NHỎ</t>
+        </is>
+      </c>
+      <c r="C17" s="49" t="inlineStr">
+        <is>
+          <t>zaloOutMergeSched ép mọi tin cuộn về kênh NGAY</t>
+        </is>
+      </c>
+      <c r="D17" s="51" t="inlineStr">
+        <is>
+          <t>js/21-notify.js:628</t>
+        </is>
+      </c>
+      <c r="E17" s="35" t="inlineStr">
+        <is>
+          <t>host.pri='now' gán cứng.</t>
+        </is>
+      </c>
+      <c r="F17" s="35" t="inlineStr">
+        <is>
+          <t>Tin lịch vốn ở kênh GỘP mà lọt vào cùng bó thì bị nâng lên gửi ngay, kể cả trong giờ im lặng.</t>
+        </is>
+      </c>
+      <c r="G17" s="52" t="inlineStr">
+        <is>
+          <t>Đ2</t>
+        </is>
+      </c>
+      <c r="H17" s="36" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF2E7D32"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>ĐỀ XUẤT CHỈNH + BỐN VIỆC CẦN BẠN CHỐT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>Nguyên tắc dẫn đường: người đọc phải ĐOÁN ĐƯỢC khi nào tin tới, và MỘT VIỆC CHỈ ĐƯỢC NÓI MỘT LẦN. Mọi mục dưới đây phục vụ đúng hai câu đó. Xếp theo thứ tự nên làm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>Chưa sửa dòng mã nào — chờ bạn duyệt. Điền ý kiến vào cột màu vàng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31.5" customHeight="1">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>Việc</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>Làm gì cụ thể</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>Sửa ở đâu</t>
+        </is>
+      </c>
+      <c r="E5" s="32" t="inlineStr">
+        <is>
+          <t>Sửa được điểm loạn</t>
+        </is>
+      </c>
+      <c r="F5" s="32" t="inlineStr">
+        <is>
+          <t>★ DUYỆT / Ý KIẾN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21.75" customHeight="1">
+      <c r="A6" s="33" t="inlineStr">
+        <is>
+          <t>A — LÀM ĐƯỢC NGAY, KHÔNG CẦN BẠN QUYẾT GÌ</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="n"/>
+      <c r="C6" s="34" t="n"/>
+      <c r="D6" s="34" t="n"/>
+      <c r="E6" s="34" t="n"/>
+      <c r="F6" s="34" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="49" t="inlineStr">
+        <is>
+          <t>Đ1</t>
+        </is>
+      </c>
+      <c r="B7" s="49" t="inlineStr">
+        <is>
+          <t>Bản tin 08:00 lọc trùng trước khi nối dòng</t>
+        </is>
+      </c>
+      <c r="C7" s="35" t="inlineStr">
+        <is>
+          <t>Trong digestBuild(), gom các mục cùng reqId (hoặc cùng fp nếu không có reqId) thành MỘT khối, đúng cách dgReviewLines() đang dùng sổ seen[id]. Danh sách người nhận gộp thành một dòng "For: …" nếu cần.</t>
+        </is>
+      </c>
+      <c r="D7" s="51" t="inlineStr">
+        <is>
+          <t>js/21-notify.js:1049 · ~10 dòng</t>
+        </is>
+      </c>
+      <c r="E7" s="52" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="F7" s="53" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="49" t="inlineStr">
+        <is>
+          <t>Đ5</t>
+        </is>
+      </c>
+      <c r="B8" s="49" t="inlineStr">
+        <is>
+          <t>Sửa zaloOutMergeSame + gộp theo group thay vì title</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="inlineStr">
+        <is>
+          <t>Luôn ghi byKey[k]=it khi chưa có mục nào cùng tiêu đề. Sau khi làm Đ4 (tiêu đề cố định) thì bỏ hẳn điều kiện so tiêu đề — cùng group là cùng loại việc.</t>
+        </is>
+      </c>
+      <c r="D8" s="51" t="inlineStr">
+        <is>
+          <t>js/21-notify.js:692 · 2 dòng</t>
+        </is>
+      </c>
+      <c r="E8" s="52" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="F8" s="53" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="49" t="inlineStr">
+        <is>
+          <t>Đ9</t>
+        </is>
+      </c>
+      <c r="B9" s="49" t="inlineStr">
+        <is>
+          <t>Mở digestStale cho approved và cancelled</t>
+        </is>
+      </c>
+      <c r="C9" s="35" t="inlineStr">
+        <is>
+          <t>Thêm: 'approved' lỗi thời khi đơn không còn status==='approved'. ('cancelled' đã có nhánh 'req' lo khi đơn bị xoá hẳn.)</t>
+        </is>
+      </c>
+      <c r="D9" s="51" t="inlineStr">
+        <is>
+          <t>js/21-notify.js:903 · ~4 dòng</t>
+        </is>
+      </c>
+      <c r="E9" s="52" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+      <c r="F9" s="53" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="49" t="inlineStr">
+        <is>
+          <t>Đ7</t>
+        </is>
+      </c>
+      <c r="B10" s="49" t="inlineStr">
+        <is>
+          <t>Link app chỉ in ở tin cần bấm vào app</t>
+        </is>
+      </c>
+      <c r="C10" s="35" t="inlineStr">
+        <is>
+          <t>Điều kiện: chỉ push APP_URL khi first.action có giá trị. Tin kết quả duyệt, thông báo chung, bản tin sáng không cần link — cắt được khoảng một nửa số khung xem trước trong chat.</t>
+        </is>
+      </c>
+      <c r="D10" s="51" t="inlineStr">
+        <is>
+          <t>Code-MOI.gs:461 · 1 dòng · CẦN DEPLOY LẠI APPS SCRIPT</t>
+        </is>
+      </c>
+      <c r="E10" s="52" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
+      <c r="F10" s="53" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="49" t="inlineStr">
+        <is>
+          <t>Đ8</t>
+        </is>
+      </c>
+      <c r="B11" s="49" t="inlineStr">
+        <is>
+          <t>Rút emoji về 5 nhóm, khớp đúng với khoá group</t>
+        </is>
+      </c>
+      <c r="C11" s="35" t="inlineStr">
+        <is>
+          <t>📅 lịch &amp; ca  ·  📥 cần duyệt  ·  ✅ kết quả đơn (❌ khi xấu)  ·  🙋 nhờ người / xác nhận  ·  📢 thông báo chung. Liếc một giây là biết tin thuộc nhóm nào; chi tiết để chữ nói.</t>
+        </is>
+      </c>
+      <c r="D11" s="51" t="inlineStr">
+        <is>
+          <t>js/21-notify.js:215 ZALO_TITLE</t>
+        </is>
+      </c>
+      <c r="E11" s="52" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+      <c r="F11" s="53" t="inlineStr"/>
+    </row>
+    <row r="12" ht="21.75" customHeight="1">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>B — ĐỔI CƠ CHẾ, CẦN BẠN CHỐT MỤC C TRƯỚC</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="n"/>
+      <c r="C12" s="34" t="n"/>
+      <c r="D12" s="34" t="n"/>
+      <c r="E12" s="34" t="n"/>
+      <c r="F12" s="34" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="49" t="inlineStr">
+        <is>
+          <t>Đ2</t>
+        </is>
+      </c>
+      <c r="B13" s="49" t="inlineStr">
+        <is>
+          <t>Rút còn HAI nhịp: GẤP và BẢN TIN — bỏ hẳn kênh GỘP 8 phút</t>
+        </is>
+      </c>
+      <c r="C13" s="35" t="inlineStr">
+        <is>
+          <t>GẤP (≤60 giây, CÓ áp giờ im lặng) — chỉ việc mà biết muộn là đi làm sai giờ: schedChange, schedBulk, schedRevoke, swapConfirm, coverConfirm, swapNo, coverNo, rejected, revoked.   ///   BẢN TIN (gom 08:00, và 16:00 nếu chọn 2 lần/ngày) — mọi thứ giấy tờ: apprNeed, approved, cancelled, finalNote, coverRemoved, schedDecline, event, training.   ///   Kênh GỘP 8 phút hiện không gom được gì thật — nó chỉ làm tin tới trễ một cách ngẫu nhiên.</t>
+        </is>
+      </c>
+      <c r="D13" s="51" t="inlineStr">
+        <is>
+          <t>ZALO_CHANNEL + ZALO_INFO_CHANNEL (js/21-notify.js:49–161) + Code-MOI.gs</t>
+        </is>
+      </c>
+      <c r="E13" s="52" t="inlineStr">
+        <is>
+          <t>L2, L3, L12</t>
+        </is>
+      </c>
+      <c r="F13" s="53" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="49" t="inlineStr">
+        <is>
+          <t>Đ3</t>
+        </is>
+      </c>
+      <c r="B14" s="49" t="inlineStr">
+        <is>
+          <t>Bỏ DIGEST_REQ_TYPES — kênh quyết theo LOẠI TIN, không theo loại đơn</t>
+        </is>
+      </c>
+      <c r="C14" s="35" t="inlineStr">
+        <is>
+          <t>Sau Đ2 thì digestApplies() chỉ còn một việc: tin có thuộc nhóm BẢN TIN không. Hết cảnh cùng tiêu đề "✅ APPROVED" mà đơn nghỉ phép tới ngay còn đơn OT tới sáng mai.</t>
+        </is>
+      </c>
+      <c r="D14" s="51" t="inlineStr">
+        <is>
+          <t>js/21-notify.js:840 · xoá được cả hằng DIGEST_REQ_TYPES</t>
+        </is>
+      </c>
+      <c r="E14" s="52" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F14" s="53" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="49" t="inlineStr">
+        <is>
+          <t>Đ4</t>
+        </is>
+      </c>
+      <c r="B15" s="49" t="inlineStr">
+        <is>
+          <t>Tiêu đề CỐ ĐỊNH — số liệu động chuyển xuống dòng đầu thân tin</t>
+        </is>
+      </c>
+      <c r="C15" s="35" t="inlineStr">
+        <is>
+          <t>"📅 SCHEDULE UPDATED" thay vì "📅 SCHEDULE UPDATED — 3 people / 7 changes"; số người/số ô thành dòng đầu của thân tin. Tương tự với cấp duyệt của apprNeed và đuôi "· 5 item(s) · 12/08" của bản tin. Cả zaloFp lẫn khoá gộp của Apps Script lập tức chạy đúng trở lại.</t>
+        </is>
+      </c>
+      <c r="D15" s="51" t="inlineStr">
+        <is>
+          <t>js/21-notify.js:510 zaloTitle() + digestBuild()</t>
+        </is>
+      </c>
+      <c r="E15" s="52" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="F15" s="53" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="49" t="inlineStr">
+        <is>
+          <t>Đ6</t>
+        </is>
+      </c>
+      <c r="B16" s="49" t="inlineStr">
+        <is>
+          <t>Một kiểu xưng người nhận duy nhất</t>
+        </is>
+      </c>
+      <c r="C16" s="35" t="inlineStr">
+        <is>
+          <t>Chat là chat chung nên bỏ hẳn "👤". Thay bằng đúng một quy ước: tin cần ai đó bấm thì dòng thứ hai là "Cần: &lt;tên&gt;" (hoặc danh sách tên); tin chỉ để biết thì không ghi tên người nhận — tên đã nằm trong dòng dữ liệu rồi.</t>
+        </is>
+      </c>
+      <c r="D16" s="51" t="inlineStr">
+        <is>
+          <t>Code-MOI.gs buildText_() + zaloAudienceName() · CẦN DEPLOY LẠI</t>
+        </is>
+      </c>
+      <c r="E16" s="52" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="F16" s="53" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="49" t="inlineStr">
+        <is>
+          <t>Đ10</t>
+        </is>
+      </c>
+      <c r="B17" s="49" t="inlineStr">
+        <is>
+          <t>Một đồng hồ duy nhất</t>
+        </is>
+      </c>
+      <c r="C17" s="35" t="inlineStr">
+        <is>
+          <t>Đặt cứng Asia/Ho_Chi_Minh ở Apps Script thay vì Session.getScriptTimeZone(), và cho DIGEST_HOUR đọc giờ theo cùng múi thay vì giờ máy nhân viên. Nếu không, hai máy ở hai cấu hình giờ khác nhau sẽ hiểu khác ngày.</t>
+        </is>
+      </c>
+      <c r="D17" s="51" t="inlineStr">
+        <is>
+          <t>Code-MOI.gs:466 + js/21-notify.js digestDayKey()</t>
+        </is>
+      </c>
+      <c r="E17" s="52" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="F17" s="53" t="inlineStr"/>
+    </row>
+    <row r="19" ht="21.75" customHeight="1">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>C — BỐN VIỆC CẦN BẠN CHỐT  (điền vào cột F)</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="34" t="n"/>
+      <c r="E19" s="34" t="n"/>
+      <c r="F19" s="34" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="49" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B20" s="49" t="inlineStr">
+        <is>
+          <t>Mấy bản tin gom một ngày?</t>
+        </is>
+      </c>
+      <c r="C20" s="35" t="inlineStr">
+        <is>
+          <t>A: một — 08:00.   B: hai — 08:00 và 16:00.</t>
+        </is>
+      </c>
+      <c r="D20" s="35" t="inlineStr"/>
+      <c r="E20" s="54" t="inlineStr">
+        <is>
+          <t>ĐỀ XUẤT: B — đơn gửi buổi sáng không phải chờ tới hôm sau mới có ai duyệt.</t>
+        </is>
+      </c>
+      <c r="F20" s="55" t="inlineStr">
+        <is>
+          <t>← TRẢ LỜI VÀO Ô NÀY</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="49" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B21" s="49" t="inlineStr">
+        <is>
+          <t>Đơn nghỉ phép / đổi ca duyệt xong: báo ngay hay vào bản tin?</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="inlineStr">
+        <is>
+          <t>A: ngay — vì đổi lịch đi làm thật.   B: vào bản tin — thống nhất với OT.</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="inlineStr"/>
+      <c r="E21" s="54" t="inlineStr">
+        <is>
+          <t>ĐỀ XUẤT: A, nhưng khi đó tiêu đề phải KHÁC HẲN tin OT để người đọc thấy được luật.</t>
+        </is>
+      </c>
+      <c r="F21" s="55" t="inlineStr">
+        <is>
+          <t>← TRẢ LỜI VÀO Ô NÀY</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="49" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="B22" s="49" t="inlineStr">
+        <is>
+          <t>Giờ im lặng 21:30–06:30 có áp cho tin GẤP không?</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="inlineStr">
+        <is>
+          <t>A: có — im hẳn.   B: không — đổi ca gấp 22h vẫn phải tới.</t>
+        </is>
+      </c>
+      <c r="D22" s="35" t="inlineStr"/>
+      <c r="E22" s="54" t="inlineStr">
+        <is>
+          <t>ĐỀ XUẤT: A với ngoại lệ — tin của hôm nay hoặc ngày mai thì phá lệ gửi luôn, tin của ngày kia trở đi giữ tới 06:30. (Liên quan Q1 cũ ở sheet 4: ca đêm N làm 20:00–08:00.)</t>
+        </is>
+      </c>
+      <c r="F22" s="55" t="inlineStr">
+        <is>
+          <t>← TRẢ LỜI VÀO Ô NÀY</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="49" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="B23" s="49" t="inlineStr">
+        <is>
+          <t>Có giữ dòng "👤 Tên" không?</t>
+        </is>
+      </c>
+      <c r="C23" s="35" t="inlineStr">
+        <is>
+          <t>A: bỏ hẳn.   B: giữ, đổi thành "Cần: &lt;tên&gt;" và chỉ ở tin phải bấm.</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="inlineStr"/>
+      <c r="E23" s="54" t="inlineStr">
+        <is>
+          <t>ĐỀ XUẤT: B — vẫn cần một chỗ cố định để dò tên, nhưng chỉ ở tin phải bấm.</t>
+        </is>
+      </c>
+      <c r="F23" s="55" t="inlineStr">
+        <is>
+          <t>← TRẢ LỜI VÀO Ô NÀY</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="21.75" customHeight="1">
+      <c r="A25" s="56" t="inlineStr">
+        <is>
+          <t>NẾU CHỈ LÀM ĐƯỢC MỘT VIỆC: làm Đ1. Khoảng 10 dòng mã, không đụng Apps Script, không đổi hợp đồng dữ liệu, và cắt ngay phần lặp thấy rõ nhất mỗi sáng.</t>
+        </is>
+      </c>
+      <c r="B25" s="34" t="n"/>
+      <c r="C25" s="34" t="n"/>
+      <c r="D25" s="34" t="n"/>
+      <c r="E25" s="34" t="n"/>
+      <c r="F25" s="34" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A25:F25"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>